--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>退货单号</t>
   </si>
@@ -50,6 +50,9 @@
     <t>订单金额</t>
   </si>
   <si>
+    <t>退货物流单号</t>
+  </si>
+  <si>
     <t>退货类型</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>{.completeOrderAmount}</t>
+  </si>
+  <si>
+    <t>{.returnLogisticCode}</t>
   </si>
   <si>
     <t>{.typeName}</t>
@@ -1138,14 +1144,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="23" width="20.625" customWidth="1"/>
+    <col min="7" max="24" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,10 +1176,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1215,76 +1221,82 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>退货单号</t>
   </si>
@@ -92,6 +92,12 @@
     <t>备注</t>
   </si>
   <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
+  </si>
+  <si>
     <t>系统创建时间</t>
   </si>
   <si>
@@ -162,6 +168,12 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.sysCreateTime}</t>
@@ -1144,14 +1156,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="24" width="20.625" customWidth="1"/>
+    <col min="7" max="26" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,79 +1236,91 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoB2cReturnOrder.xlsx
@@ -11,6 +11,167 @@
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t>退货单号</t>
+  </si>
+  <si>
+    <t>平台退货单号</t>
+  </si>
+  <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
+    <t>销售单号</t>
+  </si>
+  <si>
+    <t>平台</t>
+  </si>
+  <si>
+    <t>店铺</t>
+  </si>
+  <si>
+    <t>订单金额</t>
+  </si>
+  <si>
+    <t>退货物流单号</t>
+  </si>
+  <si>
+    <t>退货类型</t>
+  </si>
+  <si>
+    <t>退货原因</t>
+  </si>
+  <si>
+    <t>退货状态</t>
+  </si>
+  <si>
+    <t>关联入库单号</t>
+  </si>
+  <si>
+    <t>平台SKU</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>入库状态</t>
+  </si>
+  <si>
+    <t>销售数量</t>
+  </si>
+  <si>
+    <t>退货数量</t>
+  </si>
+  <si>
+    <t>出库数量</t>
+  </si>
+  <si>
+    <t>入库数量</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>平台状态</t>
+  </si>
+  <si>
+    <t>系统创建时间</t>
+  </si>
+  <si>
+    <t>系统退货时间</t>
+  </si>
+  <si>
+    <t>系统入库时间</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.platformReturnNo}</t>
+  </si>
+  <si>
+    <t>{.platformOrderNo}</t>
+  </si>
+  <si>
+    <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.platformName}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
+  </si>
+  <si>
+    <t>{.completeOrderAmount}</t>
+  </si>
+  <si>
+    <t>{.returnLogisticCode}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.reason}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.instockCode}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.instockStatusName}</t>
+  </si>
+  <si>
+    <t>{.saleQty}</t>
+  </si>
+  <si>
+    <t>{.returnQty}</t>
+  </si>
+  <si>
+    <t>{.outQty}</t>
+  </si>
+  <si>
+    <t>{.instockQty}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.platformStatus}</t>
+  </si>
+  <si>
+    <t>{.sysCreateTime}</t>
+  </si>
+  <si>
+    <t>{.sysReturnTime}</t>
+  </si>
+  <si>
+    <t>{.sysInstockTime}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1052,267 +1213,163 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>退货单号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>平台退货单号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>平台订单编号</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>销售单号</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>店铺</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>订单金额</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>退货物流单号</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>退货类型</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>退货原因</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>退货状态</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>关联入库单号</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>平台SKU</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>入库状态</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>销售数量</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>退货数量</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>出库数量</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>入库数量</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>创建人</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>平台状态</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>系统创建时间</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>系统退货时间</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>系统入库时间</t>
-        </is>
+      <c s="1" t="s">
+        <v>0</v>
+      </c>
+      <c s="1" t="s">
+        <v>1</v>
+      </c>
+      <c s="1" t="s">
+        <v>2</v>
+      </c>
+      <c s="1" t="s">
+        <v>3</v>
+      </c>
+      <c s="1" t="s">
+        <v>4</v>
+      </c>
+      <c s="1" t="s">
+        <v>5</v>
+      </c>
+      <c s="1" t="s">
+        <v>6</v>
+      </c>
+      <c s="1" t="s">
+        <v>7</v>
+      </c>
+      <c s="1" t="s">
+        <v>8</v>
+      </c>
+      <c s="2" t="s">
+        <v>9</v>
+      </c>
+      <c s="1" t="s">
+        <v>10</v>
+      </c>
+      <c s="1" t="s">
+        <v>11</v>
+      </c>
+      <c s="1" t="s">
+        <v>12</v>
+      </c>
+      <c s="1" t="s">
+        <v>13</v>
+      </c>
+      <c s="1" t="s">
+        <v>14</v>
+      </c>
+      <c s="1" t="s">
+        <v>15</v>
+      </c>
+      <c s="1" t="s">
+        <v>16</v>
+      </c>
+      <c s="1" t="s">
+        <v>17</v>
+      </c>
+      <c s="1" t="s">
+        <v>18</v>
+      </c>
+      <c s="1" t="s">
+        <v>19</v>
+      </c>
+      <c s="1" t="s">
+        <v>20</v>
+      </c>
+      <c s="1" t="s">
+        <v>21</v>
+      </c>
+      <c s="1" t="s">
+        <v>22</v>
+      </c>
+      <c s="1" t="s">
+        <v>23</v>
+      </c>
+      <c s="1" t="s">
+        <v>24</v>
+      </c>
+      <c s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>{.code}</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformReturnNo}</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformOrderNo}</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>{.soCode}</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformName}</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>{.shopName}</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>{.completeOrderAmount}</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>{.returnLogisticCode}</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>{.typeName}</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>{.reason}</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>{.statusName}</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>{.instockCode}</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformSkuNo}</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>{.skuNo}</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>{.productName}</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>{.instockStatusName}</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>{.saleQty}</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>{.returnQty}</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t>{.outQty}</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t>{.instockQty}</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t>{.remark}</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="inlineStr">
-        <is>
-          <t>{.createUserName}</t>
-        </is>
-      </c>
-      <c r="W2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformStatus}</t>
-        </is>
-      </c>
-      <c r="X2" s="1" t="inlineStr">
-        <is>
-          <t>{.sysCreateTime}</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="inlineStr">
-        <is>
-          <t>{.sysReturnTime}</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="inlineStr">
-        <is>
-          <t>{.sysInstockTime}</t>
-        </is>
+      <c s="1" t="s">
+        <v>26</v>
+      </c>
+      <c s="1" t="s">
+        <v>27</v>
+      </c>
+      <c s="1" t="s">
+        <v>28</v>
+      </c>
+      <c s="1" t="s">
+        <v>29</v>
+      </c>
+      <c s="1" t="s">
+        <v>30</v>
+      </c>
+      <c s="1" t="s">
+        <v>31</v>
+      </c>
+      <c s="1" t="s">
+        <v>32</v>
+      </c>
+      <c s="1" t="s">
+        <v>33</v>
+      </c>
+      <c s="1" t="s">
+        <v>34</v>
+      </c>
+      <c s="1" t="s">
+        <v>35</v>
+      </c>
+      <c s="1" t="s">
+        <v>36</v>
+      </c>
+      <c s="1" t="s">
+        <v>37</v>
+      </c>
+      <c s="1" t="s">
+        <v>38</v>
+      </c>
+      <c s="1" t="s">
+        <v>39</v>
+      </c>
+      <c s="1" t="s">
+        <v>40</v>
+      </c>
+      <c s="1" t="s">
+        <v>41</v>
+      </c>
+      <c s="1" t="s">
+        <v>42</v>
+      </c>
+      <c s="1" t="s">
+        <v>43</v>
+      </c>
+      <c s="1" t="s">
+        <v>44</v>
+      </c>
+      <c s="1" t="s">
+        <v>45</v>
+      </c>
+      <c s="1" t="s">
+        <v>46</v>
+      </c>
+      <c s="1" t="s">
+        <v>47</v>
+      </c>
+      <c s="1" t="s">
+        <v>48</v>
+      </c>
+      <c s="1" t="s">
+        <v>49</v>
+      </c>
+      <c s="1" t="s">
+        <v>50</v>
+      </c>
+      <c s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
